--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_50/per_file_predictions_epoch_50.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_50/per_file_predictions_epoch_50.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,775 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.5702,0.1055,0.0656,0.3303</t>
-  </si>
-  <si>
-    <t>0.0082,0.0034,0.0007,0.9963</t>
-  </si>
-  <si>
-    <t>0.8240,0.0165,0.0034,0.1343</t>
-  </si>
-  <si>
-    <t>0.0286,0.0049,0.0404,0.9603</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0013,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9878,0.0080,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.9921,0.0047,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9973,0.0020,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9763,0.0163,0.0013,0.0014</t>
-  </si>
-  <si>
-    <t>0.9970,0.0010,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9979,0.0013,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8390,0.0241,0.1801,0.0011</t>
-  </si>
-  <si>
-    <t>0.3497,0.0453,0.7060,0.0028</t>
-  </si>
-  <si>
-    <t>0.0869,0.0209,0.9344,0.0001</t>
-  </si>
-  <si>
-    <t>0.4262,0.0395,0.6234,0.0160</t>
-  </si>
-  <si>
-    <t>0.6920,0.0652,0.2869,0.0032</t>
-  </si>
-  <si>
-    <t>0.0024,0.9941,0.0039,0.0003</t>
-  </si>
-  <si>
-    <t>0.0087,0.9910,0.0016,0.0001</t>
-  </si>
-  <si>
-    <t>0.0995,0.8896,0.0229,0.0005</t>
-  </si>
-  <si>
-    <t>0.0285,0.9690,0.0039,0.0006</t>
-  </si>
-  <si>
-    <t>0.0036,0.9945,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.3698,0.0362,0.6797,0.0108</t>
-  </si>
-  <si>
-    <t>0.4765,0.0048,0.5596,0.0227</t>
-  </si>
-  <si>
-    <t>0.0044,0.0020,0.9956,0.0003</t>
-  </si>
-  <si>
-    <t>0.1403,0.0132,0.7998,0.0559</t>
-  </si>
-  <si>
-    <t>0.0215,0.0218,0.9710,0.0026</t>
-  </si>
-  <si>
-    <t>0.0936,0.0064,0.9489,0.0012</t>
-  </si>
-  <si>
-    <t>0.0061,0.0009,0.9946,0.0009</t>
-  </si>
-  <si>
-    <t>0.2616,0.7352,0.0519,0.0033</t>
-  </si>
-  <si>
-    <t>0.5380,0.1213,0.3651,0.0060</t>
-  </si>
-  <si>
-    <t>0.0027,0.0159,0.9954,0.0008</t>
-  </si>
-  <si>
-    <t>0.0135,0.9252,0.1495,0.0004</t>
-  </si>
-  <si>
-    <t>0.8578,0.1588,0.0043,0.0078</t>
-  </si>
-  <si>
-    <t>0.5489,0.5658,0.0126,0.0102</t>
-  </si>
-  <si>
-    <t>0.8382,0.2263,0.0086,0.0006</t>
-  </si>
-  <si>
-    <t>0.0393,0.9088,0.1833,0.0200</t>
-  </si>
-  <si>
-    <t>0.0455,0.8711,0.0835,0.0071</t>
-  </si>
-  <si>
-    <t>0.0499,0.0704,0.8893,0.0400</t>
-  </si>
-  <si>
-    <t>0.0174,0.1405,0.9451,0.0027</t>
-  </si>
-  <si>
-    <t>0.0508,0.0041,0.9374,0.0112</t>
-  </si>
-  <si>
-    <t>0.0253,0.4302,0.8756,0.0049</t>
-  </si>
-  <si>
-    <t>0.0024,0.9920,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.0098,0.0401,0.9800,0.0018</t>
-  </si>
-  <si>
-    <t>0.2763,0.2350,0.0363,0.6864</t>
-  </si>
-  <si>
-    <t>0.0025,0.9915,0.0044,0.0009</t>
-  </si>
-  <si>
-    <t>0.0013,0.9938,0.0136,0.0003</t>
-  </si>
-  <si>
-    <t>0.0015,0.9929,0.0025,0.0034</t>
-  </si>
-  <si>
-    <t>0.0050,0.1337,0.9720,0.0039</t>
-  </si>
-  <si>
-    <t>0.0009,0.2555,0.9953,0.0000</t>
-  </si>
-  <si>
-    <t>0.0207,0.0518,0.9657,0.0045</t>
-  </si>
-  <si>
-    <t>0.1597,0.0037,0.9147,0.0015</t>
-  </si>
-  <si>
-    <t>0.0036,0.0068,0.9945,0.0007</t>
-  </si>
-  <si>
-    <t>0.0084,0.0348,0.9818,0.0005</t>
-  </si>
-  <si>
-    <t>0.9348,0.0826,0.0063,0.0017</t>
-  </si>
-  <si>
-    <t>0.9501,0.0283,0.0252,0.0008</t>
-  </si>
-  <si>
-    <t>0.9566,0.0534,0.0050,0.0011</t>
-  </si>
-  <si>
-    <t>0.0176,0.0469,0.9848,0.0014</t>
-  </si>
-  <si>
-    <t>0.9943,0.0038,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9943,0.0020,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.8887,0.1312,0.0128,0.0022</t>
-  </si>
-  <si>
-    <t>0.0014,0.3299,0.9879,0.0000</t>
-  </si>
-  <si>
-    <t>0.0121,0.0273,0.9819,0.0014</t>
-  </si>
-  <si>
-    <t>0.0032,0.0094,0.9907,0.0047</t>
-  </si>
-  <si>
-    <t>0.0002,0.9585,0.9592,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.0147,0.9927,0.0006</t>
-  </si>
-  <si>
-    <t>0.0595,0.9591,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.0076,0.9934,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.6432,0.0317,0.4787,0.0101</t>
-  </si>
-  <si>
-    <t>0.6341,0.2010,0.1934,0.0065</t>
-  </si>
-  <si>
-    <t>0.0156,0.1197,0.9678,0.0030</t>
-  </si>
-  <si>
-    <t>0.0023,0.8806,0.7949,0.0013</t>
-  </si>
-  <si>
-    <t>0.0027,0.8426,0.7822,0.0001</t>
-  </si>
-  <si>
-    <t>0.0017,0.9793,0.1913,0.0011</t>
-  </si>
-  <si>
-    <t>0.0022,0.9237,0.7705,0.0002</t>
-  </si>
-  <si>
-    <t>0.0201,0.0018,0.1894,0.9002</t>
-  </si>
-  <si>
-    <t>0.0061,0.0085,0.0005,0.9967</t>
-  </si>
-  <si>
-    <t>0.0132,0.0021,0.0004,0.9950</t>
-  </si>
-  <si>
-    <t>0.0251,0.0075,0.0007,0.9906</t>
-  </si>
-  <si>
-    <t>0.0257,0.0172,0.0087,0.9803</t>
-  </si>
-  <si>
-    <t>0.0052,0.0208,0.0009,0.9960</t>
-  </si>
-  <si>
-    <t>0.0008,0.9408,0.8469,0.0001</t>
-  </si>
-  <si>
-    <t>0.0095,0.4490,0.9447,0.0004</t>
-  </si>
-  <si>
-    <t>0.0103,0.3145,0.9448,0.0007</t>
-  </si>
-  <si>
-    <t>0.0137,0.6926,0.8493,0.0020</t>
-  </si>
-  <si>
-    <t>0.0015,0.9554,0.4873,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.9337,0.6790,0.0002</t>
-  </si>
-  <si>
-    <t>0.9825,0.0122,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.9916,0.0044,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9486,0.0615,0.0034,0.0015</t>
-  </si>
-  <si>
-    <t>0.9754,0.0254,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.9844,0.0085,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9878,0.0080,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9727,0.0252,0.0046,0.0012</t>
-  </si>
-  <si>
-    <t>0.9867,0.0030,0.0001,0.0029</t>
-  </si>
-  <si>
-    <t>0.9913,0.0040,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9954,0.0021,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9940,0.0042,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9967,0.0010,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9973,0.0006,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9927,0.0084,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0012,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9957,0.0013,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.0029,0.0009,0.9958,0.0007</t>
-  </si>
-  <si>
-    <t>0.0559,0.0809,0.9257,0.0027</t>
-  </si>
-  <si>
-    <t>0.5084,0.0975,0.3681,0.0994</t>
-  </si>
-  <si>
-    <t>0.1539,0.0124,0.8936,0.0048</t>
-  </si>
-  <si>
-    <t>0.0409,0.9598,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.0130,0.9833,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.1133,0.9217,0.0009,0.0020</t>
-  </si>
-  <si>
-    <t>0.1448,0.8914,0.0022,0.0022</t>
-  </si>
-  <si>
-    <t>0.0626,0.9503,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.0242,0.9780,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.4063,0.7220,0.0034,0.0013</t>
-  </si>
-  <si>
-    <t>0.6160,0.1418,0.2726,0.0555</t>
-  </si>
-  <si>
-    <t>0.3613,0.0932,0.6248,0.0214</t>
-  </si>
-  <si>
-    <t>0.5319,0.2127,0.2715,0.0096</t>
-  </si>
-  <si>
-    <t>0.3926,0.0619,0.6399,0.0060</t>
-  </si>
-  <si>
-    <t>0.1982,0.3062,0.0278,0.7564</t>
-  </si>
-  <si>
-    <t>0.0057,0.9821,0.0143,0.0013</t>
-  </si>
-  <si>
-    <t>0.0030,0.9897,0.0075,0.0019</t>
-  </si>
-  <si>
-    <t>0.0325,0.9191,0.0194,0.0971</t>
-  </si>
-  <si>
-    <t>0.0016,0.9688,0.6085,0.0001</t>
-  </si>
-  <si>
-    <t>0.0165,0.9783,0.0171,0.0002</t>
-  </si>
-  <si>
-    <t>0.8346,0.1528,0.0402,0.0008</t>
-  </si>
-  <si>
-    <t>0.6515,0.5133,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.9591,0.0300,0.0071,0.0020</t>
-  </si>
-  <si>
-    <t>0.9898,0.0016,0.0013,0.0027</t>
-  </si>
-  <si>
-    <t>0.9787,0.0111,0.0017,0.0038</t>
-  </si>
-  <si>
-    <t>0.9774,0.0064,0.0045,0.0044</t>
-  </si>
-  <si>
-    <t>0.9941,0.0019,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9691,0.0086,0.0047,0.0075</t>
-  </si>
-  <si>
-    <t>0.9785,0.0143,0.0053,0.0014</t>
-  </si>
-  <si>
-    <t>0.9866,0.0119,0.0011,0.0008</t>
-  </si>
-  <si>
-    <t>0.0020,0.8036,0.8978,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.5549,0.9010,0.0003</t>
-  </si>
-  <si>
-    <t>0.0900,0.2474,0.6268,0.0005</t>
-  </si>
-  <si>
-    <t>0.0230,0.1357,0.9416,0.0008</t>
-  </si>
-  <si>
-    <t>0.6700,0.1621,0.2185,0.0290</t>
-  </si>
-  <si>
-    <t>0.6080,0.0178,0.4748,0.0172</t>
-  </si>
-  <si>
-    <t>0.2199,0.0065,0.8383,0.0322</t>
-  </si>
-  <si>
-    <t>0.5564,0.2094,0.2622,0.0317</t>
-  </si>
-  <si>
-    <t>0.1498,0.0036,0.0008,0.9519</t>
-  </si>
-  <si>
-    <t>0.0007,0.0001,0.0028,0.9974</t>
-  </si>
-  <si>
-    <t>0.0037,0.0052,0.0023,0.9957</t>
-  </si>
-  <si>
-    <t>0.0048,0.0009,0.0025,0.9959</t>
-  </si>
-  <si>
-    <t>0.0055,0.9154,0.4608,0.0005</t>
-  </si>
-  <si>
-    <t>0.9914,0.0048,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.1424,0.8854,0.0061,0.0030</t>
-  </si>
-  <si>
-    <t>0.9774,0.0013,0.0009,0.0147</t>
-  </si>
-  <si>
-    <t>0.3594,0.7400,0.0107,0.0042</t>
-  </si>
-  <si>
-    <t>0.9675,0.0124,0.0143,0.0026</t>
-  </si>
-  <si>
-    <t>0.1150,0.0018,0.0040,0.9566</t>
-  </si>
-  <si>
-    <t>0.9068,0.1103,0.0052,0.0068</t>
-  </si>
-  <si>
-    <t>0.0126,0.0583,0.8192,0.2526</t>
-  </si>
-  <si>
-    <t>0.5721,0.0008,0.0049,0.5798</t>
-  </si>
-  <si>
-    <t>0.8283,0.0015,0.0092,0.1684</t>
-  </si>
-  <si>
-    <t>0.6458,0.3731,0.0266,0.0099</t>
-  </si>
-  <si>
-    <t>0.8780,0.0662,0.0581,0.0032</t>
-  </si>
-  <si>
-    <t>0.8735,0.0653,0.0583,0.0010</t>
-  </si>
-  <si>
-    <t>0.2125,0.6393,0.0253,0.1158</t>
-  </si>
-  <si>
-    <t>0.6023,0.4071,0.0447,0.0034</t>
-  </si>
-  <si>
-    <t>0.6825,0.4580,0.0056,0.0018</t>
-  </si>
-  <si>
-    <t>0.9876,0.0041,0.0012,0.0021</t>
-  </si>
-  <si>
-    <t>0.9903,0.0016,0.0003,0.0042</t>
-  </si>
-  <si>
-    <t>0.9946,0.0015,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9853,0.0013,0.0004,0.0107</t>
-  </si>
-  <si>
-    <t>0.9868,0.0041,0.0005,0.0026</t>
-  </si>
-  <si>
-    <t>0.9836,0.0112,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9922,0.0031,0.0007,0.0011</t>
-  </si>
-  <si>
-    <t>0.9940,0.0061,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.5317,0.5855,0.0083,0.0030</t>
-  </si>
-  <si>
-    <t>0.2036,0.8554,0.0055,0.0014</t>
-  </si>
-  <si>
-    <t>0.3683,0.7240,0.0076,0.0041</t>
-  </si>
-  <si>
-    <t>0.3582,0.6135,0.0805,0.0024</t>
-  </si>
-  <si>
-    <t>0.8759,0.1366,0.0083,0.0058</t>
-  </si>
-  <si>
-    <t>0.9441,0.0616,0.0075,0.0023</t>
-  </si>
-  <si>
-    <t>0.8391,0.2002,0.0154,0.0019</t>
-  </si>
-  <si>
-    <t>0.8787,0.1814,0.0060,0.0010</t>
-  </si>
-  <si>
-    <t>0.0082,0.1417,0.9871,0.0018</t>
-  </si>
-  <si>
-    <t>0.9462,0.0489,0.0109,0.0007</t>
-  </si>
-  <si>
-    <t>0.0039,0.0037,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.1419,0.9833,0.0019</t>
-  </si>
-  <si>
-    <t>0.0240,0.0342,0.9619,0.0075</t>
-  </si>
-  <si>
-    <t>0.0413,0.0681,0.9480,0.0017</t>
-  </si>
-  <si>
-    <t>0.0206,0.0614,0.9691,0.0006</t>
-  </si>
-  <si>
-    <t>0.0310,0.0032,0.9859,0.0001</t>
-  </si>
-  <si>
-    <t>0.0043,0.0052,0.9946,0.0004</t>
-  </si>
-  <si>
-    <t>0.5765,0.0956,0.3827,0.0174</t>
-  </si>
-  <si>
-    <t>0.3314,0.1158,0.6348,0.0303</t>
-  </si>
-  <si>
-    <t>0.5534,0.2127,0.2881,0.0222</t>
-  </si>
-  <si>
-    <t>0.3344,0.2428,0.3308,0.0015</t>
-  </si>
-  <si>
-    <t>0.2182,0.0325,0.8396,0.0010</t>
-  </si>
-  <si>
-    <t>0.7694,0.0243,0.2415,0.0219</t>
-  </si>
-  <si>
-    <t>0.2107,0.5792,0.2507,0.0071</t>
-  </si>
-  <si>
-    <t>0.4412,0.0877,0.5807,0.0112</t>
-  </si>
-  <si>
-    <t>0.4100,0.7309,0.0055,0.0018</t>
-  </si>
-  <si>
-    <t>0.0888,0.9271,0.0023,0.0014</t>
-  </si>
-  <si>
-    <t>0.8274,0.2808,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.8902,0.1894,0.0043,0.0005</t>
-  </si>
-  <si>
-    <t>0.8242,0.2450,0.0053,0.0024</t>
-  </si>
-  <si>
-    <t>0.5089,0.1099,0.4434,0.0030</t>
-  </si>
-  <si>
-    <t>0.8362,0.0079,0.2294,0.0029</t>
-  </si>
-  <si>
-    <t>0.5173,0.2014,0.2910,0.0405</t>
-  </si>
-  <si>
-    <t>0.5746,0.0382,0.5039,0.0153</t>
-  </si>
-  <si>
-    <t>0.2649,0.0166,0.7573,0.0234</t>
-  </si>
-  <si>
-    <t>0.0102,0.0119,0.9629,0.0384</t>
-  </si>
-  <si>
-    <t>0.0207,0.0317,0.9681,0.0050</t>
-  </si>
-  <si>
-    <t>0.0173,0.0407,0.9788,0.0026</t>
-  </si>
-  <si>
-    <t>0.1059,0.0354,0.9258,0.0029</t>
-  </si>
-  <si>
-    <t>0.0292,0.1456,0.8997,0.0029</t>
-  </si>
-  <si>
-    <t>0.9808,0.0165,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.9816,0.0264,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9849,0.0105,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.9696,0.0322,0.0037,0.0009</t>
-  </si>
-  <si>
-    <t>0.9863,0.0111,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9715,0.0258,0.0048,0.0010</t>
-  </si>
-  <si>
-    <t>0.9912,0.0046,0.0007,0.0008</t>
-  </si>
-  <si>
-    <t>0.9769,0.0227,0.0021,0.0019</t>
-  </si>
-  <si>
-    <t>0.1219,0.0094,0.9357,0.0024</t>
-  </si>
-  <si>
-    <t>0.3756,0.4391,0.2669,0.0048</t>
-  </si>
-  <si>
-    <t>0.9241,0.0190,0.0241,0.0203</t>
-  </si>
-  <si>
-    <t>0.0015,0.0074,0.9970,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0145,0.9960,0.0008</t>
-  </si>
-  <si>
-    <t>0.0128,0.0034,0.9905,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0021,0.9991,0.0003</t>
-  </si>
-  <si>
-    <t>0.0789,0.0891,0.8381,0.0148</t>
-  </si>
-  <si>
-    <t>0.0006,0.0016,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0183,0.0876,0.9410,0.0023</t>
-  </si>
-  <si>
-    <t>0.0883,0.2003,0.7847,0.0102</t>
-  </si>
-  <si>
-    <t>0.5884,0.0588,0.4213,0.0205</t>
-  </si>
-  <si>
-    <t>0.5254,0.0106,0.7070,0.0017</t>
-  </si>
-  <si>
-    <t>0.8049,0.0372,0.1434,0.0101</t>
-  </si>
-  <si>
-    <t>0.9941,0.0044,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9940,0.0082,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0032,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9189,0.1156,0.0043,0.0009</t>
-  </si>
-  <si>
-    <t>0.9906,0.0056,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9654,0.0422,0.0032,0.0006</t>
-  </si>
-  <si>
-    <t>0.9964,0.0015,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9438,0.0768,0.0047,0.0009</t>
-  </si>
-  <si>
-    <t>0.0177,0.0212,0.9759,0.0013</t>
-  </si>
-  <si>
-    <t>0.0055,0.0889,0.9815,0.0015</t>
-  </si>
-  <si>
-    <t>0.0098,0.0887,0.9712,0.0042</t>
-  </si>
-  <si>
-    <t>0.0907,0.0866,0.7969,0.0078</t>
-  </si>
-  <si>
-    <t>0.0022,0.0019,0.9968,0.0005</t>
-  </si>
-  <si>
-    <t>0.2476,0.0061,0.3517,0.3962</t>
-  </si>
-  <si>
-    <t>0.0672,0.0118,0.9246,0.0202</t>
-  </si>
-  <si>
-    <t>0.0641,0.1938,0.8682,0.0229</t>
-  </si>
-  <si>
-    <t>0.6519,0.0017,0.0566,0.2853</t>
-  </si>
-  <si>
-    <t>0.0693,0.0311,0.0148,0.9501</t>
-  </si>
-  <si>
-    <t>0.0442,0.0021,0.0020,0.9824</t>
-  </si>
-  <si>
-    <t>0.0066,0.0020,0.0012,0.9962</t>
-  </si>
-  <si>
-    <t>0.0148,0.0004,0.0006,0.9943</t>
-  </si>
-  <si>
-    <t>0.1744,0.1140,0.0052,0.8840</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.1229,0.1212,0.0026,0.8895</t>
+  </si>
+  <si>
+    <t>0.0126,0.0016,0.0025,0.9921</t>
+  </si>
+  <si>
+    <t>0.7216,0.0065,0.0102,0.2485</t>
+  </si>
+  <si>
+    <t>0.0294,0.0021,0.0062,0.9825</t>
+  </si>
+  <si>
+    <t>0.9982,0.0006,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0014,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9904,0.0034,0.0006,0.0016</t>
+  </si>
+  <si>
+    <t>0.9885,0.0045,0.0012,0.0023</t>
+  </si>
+  <si>
+    <t>0.9886,0.0102,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9827,0.0207,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.9962,0.0011,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9939,0.0041,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.2549,0.6134,0.1663,0.0296</t>
+  </si>
+  <si>
+    <t>0.0762,0.0329,0.9259,0.0022</t>
+  </si>
+  <si>
+    <t>0.0885,0.0618,0.8999,0.0008</t>
+  </si>
+  <si>
+    <t>0.0593,0.0715,0.9075,0.0041</t>
+  </si>
+  <si>
+    <t>0.8020,0.0596,0.1360,0.0030</t>
+  </si>
+  <si>
+    <t>0.0106,0.9789,0.0218,0.0002</t>
+  </si>
+  <si>
+    <t>0.0042,0.9922,0.0055,0.0003</t>
+  </si>
+  <si>
+    <t>0.3467,0.7369,0.0095,0.0012</t>
+  </si>
+  <si>
+    <t>0.1068,0.8995,0.0132,0.0006</t>
+  </si>
+  <si>
+    <t>0.0051,0.9910,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.4852,0.0103,0.6403,0.0173</t>
+  </si>
+  <si>
+    <t>0.2340,0.0174,0.8144,0.0126</t>
+  </si>
+  <si>
+    <t>0.0299,0.0084,0.9673,0.0066</t>
+  </si>
+  <si>
+    <t>0.2256,0.0097,0.8224,0.0103</t>
+  </si>
+  <si>
+    <t>0.1049,0.0303,0.8832,0.0258</t>
+  </si>
+  <si>
+    <t>0.0100,0.0012,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.0060,0.0263,0.9827,0.0083</t>
+  </si>
+  <si>
+    <t>0.3254,0.7305,0.0133,0.0037</t>
+  </si>
+  <si>
+    <t>0.2205,0.2355,0.7054,0.0097</t>
+  </si>
+  <si>
+    <t>0.0061,0.0089,0.9893,0.0037</t>
+  </si>
+  <si>
+    <t>0.0067,0.9624,0.1019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9313,0.0435,0.0037,0.0061</t>
+  </si>
+  <si>
+    <t>0.3926,0.0741,0.5762,0.0048</t>
+  </si>
+  <si>
+    <t>0.8615,0.1704,0.0123,0.0007</t>
+  </si>
+  <si>
+    <t>0.0599,0.8924,0.1597,0.0046</t>
+  </si>
+  <si>
+    <t>0.0229,0.7627,0.6120,0.0090</t>
+  </si>
+  <si>
+    <t>0.1517,0.0516,0.8908,0.0047</t>
+  </si>
+  <si>
+    <t>0.0902,0.4010,0.7230,0.0119</t>
+  </si>
+  <si>
+    <t>0.0445,0.0203,0.7740,0.2369</t>
+  </si>
+  <si>
+    <t>0.0248,0.1688,0.9488,0.0016</t>
+  </si>
+  <si>
+    <t>0.0213,0.9408,0.0598,0.0015</t>
+  </si>
+  <si>
+    <t>0.0886,0.0105,0.9160,0.0108</t>
+  </si>
+  <si>
+    <t>0.0854,0.1576,0.0956,0.8103</t>
+  </si>
+  <si>
+    <t>0.0021,0.9886,0.0067,0.0110</t>
+  </si>
+  <si>
+    <t>0.0046,0.9693,0.1576,0.0006</t>
+  </si>
+  <si>
+    <t>0.0004,0.9969,0.0052,0.0012</t>
+  </si>
+  <si>
+    <t>0.0094,0.1848,0.8737,0.0211</t>
+  </si>
+  <si>
+    <t>0.0084,0.0058,0.9950,0.0001</t>
+  </si>
+  <si>
+    <t>0.0537,0.0051,0.9516,0.0137</t>
+  </si>
+  <si>
+    <t>0.0689,0.0196,0.9368,0.0036</t>
+  </si>
+  <si>
+    <t>0.0032,0.2710,0.9831,0.0004</t>
+  </si>
+  <si>
+    <t>0.0139,0.0296,0.9825,0.0001</t>
+  </si>
+  <si>
+    <t>0.9612,0.0578,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9158,0.0728,0.0201,0.0008</t>
+  </si>
+  <si>
+    <t>0.9782,0.0151,0.0035,0.0012</t>
+  </si>
+  <si>
+    <t>0.0117,0.0440,0.9729,0.0184</t>
+  </si>
+  <si>
+    <t>0.9705,0.0357,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.9736,0.0345,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.9688,0.0257,0.0071,0.0009</t>
+  </si>
+  <si>
+    <t>0.0016,0.8987,0.9172,0.0002</t>
+  </si>
+  <si>
+    <t>0.0165,0.1136,0.9523,0.0009</t>
+  </si>
+  <si>
+    <t>0.0112,0.0242,0.9847,0.0009</t>
+  </si>
+  <si>
+    <t>0.0009,0.9414,0.8805,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.0756,0.9877,0.0008</t>
+  </si>
+  <si>
+    <t>0.0198,0.9133,0.1512,0.0007</t>
+  </si>
+  <si>
+    <t>0.0122,0.9894,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9175,0.0157,0.0857,0.0011</t>
+  </si>
+  <si>
+    <t>0.5403,0.4317,0.0434,0.0006</t>
+  </si>
+  <si>
+    <t>0.2949,0.2873,0.3380,0.0026</t>
+  </si>
+  <si>
+    <t>0.0031,0.5976,0.9278,0.0002</t>
+  </si>
+  <si>
+    <t>0.0218,0.7542,0.5383,0.0017</t>
+  </si>
+  <si>
+    <t>0.0010,0.9859,0.1211,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9073,0.8977,0.0002</t>
+  </si>
+  <si>
+    <t>0.0116,0.0011,0.0195,0.9782</t>
+  </si>
+  <si>
+    <t>0.0043,0.0155,0.0010,0.9960</t>
+  </si>
+  <si>
+    <t>0.0038,0.0724,0.0008,0.9962</t>
+  </si>
+  <si>
+    <t>0.0233,0.0117,0.0022,0.9879</t>
+  </si>
+  <si>
+    <t>0.0367,0.0284,0.0053,0.9774</t>
+  </si>
+  <si>
+    <t>0.0215,0.0112,0.0038,0.9864</t>
+  </si>
+  <si>
+    <t>0.0008,0.9173,0.8890,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.5502,0.9898,0.0001</t>
+  </si>
+  <si>
+    <t>0.0061,0.9306,0.3111,0.0005</t>
+  </si>
+  <si>
+    <t>0.0174,0.3440,0.9006,0.0011</t>
+  </si>
+  <si>
+    <t>0.0016,0.8222,0.9087,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.9003,0.8864,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0020,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9910,0.0041,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9613,0.0426,0.0047,0.0010</t>
+  </si>
+  <si>
+    <t>0.9911,0.0065,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9293,0.1011,0.0048,0.0009</t>
+  </si>
+  <si>
+    <t>0.9847,0.0139,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9673,0.0298,0.0046,0.0011</t>
+  </si>
+  <si>
+    <t>0.9884,0.0091,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9946,0.0034,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9876,0.0106,0.0016,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0011,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9918,0.0070,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9144,0.1173,0.0074,0.0010</t>
+  </si>
+  <si>
+    <t>0.9887,0.0068,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.0048,0.0027,0.9941,0.0009</t>
+  </si>
+  <si>
+    <t>0.0306,0.0088,0.9752,0.0021</t>
+  </si>
+  <si>
+    <t>0.7562,0.0093,0.2925,0.0106</t>
+  </si>
+  <si>
+    <t>0.1100,0.0024,0.9441,0.0009</t>
+  </si>
+  <si>
+    <t>0.0332,0.9622,0.0051,0.0011</t>
+  </si>
+  <si>
+    <t>0.0194,0.9787,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.0936,0.8997,0.0087,0.0032</t>
+  </si>
+  <si>
+    <t>0.3594,0.7252,0.0149,0.0023</t>
+  </si>
+  <si>
+    <t>0.0272,0.9676,0.0032,0.0007</t>
+  </si>
+  <si>
+    <t>0.0034,0.9925,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.2494,0.8242,0.0104,0.0012</t>
+  </si>
+  <si>
+    <t>0.7982,0.0369,0.1892,0.0214</t>
+  </si>
+  <si>
+    <t>0.4005,0.0146,0.7489,0.0067</t>
+  </si>
+  <si>
+    <t>0.1643,0.7772,0.0700,0.0110</t>
+  </si>
+  <si>
+    <t>0.1789,0.1717,0.6891,0.0136</t>
+  </si>
+  <si>
+    <t>0.0144,0.1189,0.0142,0.9746</t>
+  </si>
+  <si>
+    <t>0.0013,0.9952,0.0118,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.9837,0.0068,0.0116</t>
+  </si>
+  <si>
+    <t>0.0323,0.8776,0.0192,0.2091</t>
+  </si>
+  <si>
+    <t>0.0034,0.9800,0.0472,0.0034</t>
+  </si>
+  <si>
+    <t>0.0035,0.9897,0.0381,0.0001</t>
+  </si>
+  <si>
+    <t>0.8431,0.1591,0.0243,0.0011</t>
+  </si>
+  <si>
+    <t>0.7446,0.3655,0.0093,0.0006</t>
+  </si>
+  <si>
+    <t>0.9172,0.0671,0.0228,0.0043</t>
+  </si>
+  <si>
+    <t>0.9925,0.0040,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.9931,0.0018,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9809,0.0093,0.0033,0.0017</t>
+  </si>
+  <si>
+    <t>0.9940,0.0011,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9695,0.0251,0.0058,0.0012</t>
+  </si>
+  <si>
+    <t>0.9598,0.0160,0.0081,0.0082</t>
+  </si>
+  <si>
+    <t>0.9699,0.0158,0.0072,0.0031</t>
+  </si>
+  <si>
+    <t>0.0006,0.8687,0.9214,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.8130,0.8056,0.0005</t>
+  </si>
+  <si>
+    <t>0.0212,0.2863,0.8630,0.0010</t>
+  </si>
+  <si>
+    <t>0.0539,0.0300,0.9531,0.0011</t>
+  </si>
+  <si>
+    <t>0.4732,0.4726,0.0653,0.0936</t>
+  </si>
+  <si>
+    <t>0.3219,0.0326,0.7770,0.0031</t>
+  </si>
+  <si>
+    <t>0.8258,0.0032,0.3886,0.0009</t>
+  </si>
+  <si>
+    <t>0.3933,0.4556,0.1831,0.0544</t>
+  </si>
+  <si>
+    <t>0.4095,0.0038,0.0206,0.6897</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.0006,0.9989</t>
+  </si>
+  <si>
+    <t>0.0074,0.0156,0.0085,0.9878</t>
+  </si>
+  <si>
+    <t>0.0282,0.0024,0.0057,0.9827</t>
+  </si>
+  <si>
+    <t>0.0022,0.9468,0.6567,0.0005</t>
+  </si>
+  <si>
+    <t>0.9708,0.0204,0.0046,0.0028</t>
+  </si>
+  <si>
+    <t>0.1340,0.9067,0.0022,0.0023</t>
+  </si>
+  <si>
+    <t>0.9823,0.0054,0.0002,0.0062</t>
+  </si>
+  <si>
+    <t>0.2810,0.8322,0.0035,0.0018</t>
+  </si>
+  <si>
+    <t>0.9763,0.0031,0.0015,0.0081</t>
+  </si>
+  <si>
+    <t>0.6891,0.0078,0.0445,0.3057</t>
+  </si>
+  <si>
+    <t>0.9683,0.0203,0.0053,0.0029</t>
+  </si>
+  <si>
+    <t>0.0245,0.0407,0.9007,0.0905</t>
+  </si>
+  <si>
+    <t>0.6480,0.0078,0.0110,0.3845</t>
+  </si>
+  <si>
+    <t>0.9724,0.0026,0.0033,0.0092</t>
+  </si>
+  <si>
+    <t>0.4721,0.4988,0.1028,0.0193</t>
+  </si>
+  <si>
+    <t>0.9505,0.0507,0.0036,0.0018</t>
+  </si>
+  <si>
+    <t>0.9391,0.0331,0.0200,0.0006</t>
+  </si>
+  <si>
+    <t>0.2466,0.7580,0.0329,0.0062</t>
+  </si>
+  <si>
+    <t>0.8638,0.0932,0.0314,0.0070</t>
+  </si>
+  <si>
+    <t>0.8076,0.0718,0.1450,0.0317</t>
+  </si>
+  <si>
+    <t>0.9890,0.0022,0.0009,0.0027</t>
+  </si>
+  <si>
+    <t>0.9921,0.0033,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9906,0.0050,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9903,0.0022,0.0010,0.0021</t>
+  </si>
+  <si>
+    <t>0.9732,0.0285,0.0039,0.0013</t>
+  </si>
+  <si>
+    <t>0.9847,0.0090,0.0023,0.0016</t>
+  </si>
+  <si>
+    <t>0.9935,0.0021,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9831,0.0151,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.7206,0.4476,0.0031,0.0008</t>
+  </si>
+  <si>
+    <t>0.7589,0.4008,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.6600,0.5027,0.0055,0.0015</t>
+  </si>
+  <si>
+    <t>0.5327,0.4541,0.0718,0.0114</t>
+  </si>
+  <si>
+    <t>0.9567,0.0670,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.9552,0.0375,0.0047,0.0020</t>
+  </si>
+  <si>
+    <t>0.9405,0.0626,0.0091,0.0008</t>
+  </si>
+  <si>
+    <t>0.8530,0.1442,0.0225,0.0065</t>
+  </si>
+  <si>
+    <t>0.0010,0.1023,0.9951,0.0005</t>
+  </si>
+  <si>
+    <t>0.9520,0.0280,0.0198,0.0005</t>
+  </si>
+  <si>
+    <t>0.0062,0.0023,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0027,0.0840,0.9903,0.0004</t>
+  </si>
+  <si>
+    <t>0.2857,0.0913,0.7003,0.0171</t>
+  </si>
+  <si>
+    <t>0.0180,0.6669,0.6608,0.0016</t>
+  </si>
+  <si>
+    <t>0.0145,0.0063,0.9903,0.0005</t>
+  </si>
+  <si>
+    <t>0.0068,0.0008,0.9967,0.0001</t>
+  </si>
+  <si>
+    <t>0.0181,0.0195,0.9785,0.0016</t>
+  </si>
+  <si>
+    <t>0.1288,0.0312,0.8843,0.0087</t>
+  </si>
+  <si>
+    <t>0.1569,0.0637,0.8308,0.0045</t>
+  </si>
+  <si>
+    <t>0.5913,0.0988,0.3832,0.0150</t>
+  </si>
+  <si>
+    <t>0.3267,0.0847,0.6094,0.0013</t>
+  </si>
+  <si>
+    <t>0.1409,0.6482,0.1373,0.0003</t>
+  </si>
+  <si>
+    <t>0.5114,0.1102,0.4140,0.0020</t>
+  </si>
+  <si>
+    <t>0.5627,0.2589,0.2561,0.0323</t>
+  </si>
+  <si>
+    <t>0.2404,0.1079,0.5894,0.0006</t>
+  </si>
+  <si>
+    <t>0.6535,0.4944,0.0057,0.0016</t>
+  </si>
+  <si>
+    <t>0.6860,0.4975,0.0033,0.0022</t>
+  </si>
+  <si>
+    <t>0.2409,0.7898,0.0102,0.0056</t>
+  </si>
+  <si>
+    <t>0.9577,0.0575,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.7056,0.4721,0.0043,0.0015</t>
+  </si>
+  <si>
+    <t>0.5126,0.0758,0.4874,0.0050</t>
+  </si>
+  <si>
+    <t>0.7260,0.0707,0.2221,0.0047</t>
+  </si>
+  <si>
+    <t>0.5405,0.2131,0.2027,0.0388</t>
+  </si>
+  <si>
+    <t>0.6818,0.0069,0.4699,0.0063</t>
+  </si>
+  <si>
+    <t>0.8435,0.0114,0.1728,0.0033</t>
+  </si>
+  <si>
+    <t>0.0057,0.0253,0.9762,0.0176</t>
+  </si>
+  <si>
+    <t>0.0224,0.3807,0.8256,0.0135</t>
+  </si>
+  <si>
+    <t>0.1242,0.0213,0.9200,0.0038</t>
+  </si>
+  <si>
+    <t>0.0371,0.1976,0.9188,0.0040</t>
+  </si>
+  <si>
+    <t>0.0588,0.3655,0.7393,0.0017</t>
+  </si>
+  <si>
+    <t>0.9626,0.0402,0.0073,0.0003</t>
+  </si>
+  <si>
+    <t>0.9813,0.0226,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.9722,0.0117,0.0007,0.0049</t>
+  </si>
+  <si>
+    <t>0.9812,0.0246,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.9817,0.0157,0.0025,0.0007</t>
+  </si>
+  <si>
+    <t>0.9955,0.0023,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9890,0.0083,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9747,0.0266,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.0731,0.0958,0.8862,0.0080</t>
+  </si>
+  <si>
+    <t>0.2284,0.5419,0.3144,0.0063</t>
+  </si>
+  <si>
+    <t>0.9144,0.0188,0.0399,0.0118</t>
+  </si>
+  <si>
+    <t>0.0070,0.0197,0.9908,0.0004</t>
+  </si>
+  <si>
+    <t>0.0020,0.0026,0.9973,0.0004</t>
+  </si>
+  <si>
+    <t>0.0150,0.1382,0.9499,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.0018,0.9985,0.0004</t>
+  </si>
+  <si>
+    <t>0.0107,0.2031,0.9203,0.0032</t>
+  </si>
+  <si>
+    <t>0.0009,0.0026,0.9985,0.0004</t>
+  </si>
+  <si>
+    <t>0.0115,0.2552,0.9187,0.0054</t>
+  </si>
+  <si>
+    <t>0.0782,0.5300,0.5499,0.0096</t>
+  </si>
+  <si>
+    <t>0.5914,0.0124,0.4645,0.0193</t>
+  </si>
+  <si>
+    <t>0.3576,0.0165,0.7612,0.0026</t>
+  </si>
+  <si>
+    <t>0.8923,0.0107,0.1124,0.0025</t>
+  </si>
+  <si>
+    <t>0.9839,0.0170,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9884,0.0081,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9936,0.0032,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9867,0.0154,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.9868,0.0029,0.0006,0.0027</t>
+  </si>
+  <si>
+    <t>0.9863,0.0143,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0008,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9906,0.0055,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.0234,0.0577,0.9665,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.0295,0.9936,0.0008</t>
+  </si>
+  <si>
+    <t>0.0251,0.3585,0.8247,0.0022</t>
+  </si>
+  <si>
+    <t>0.1539,0.0253,0.8770,0.0016</t>
+  </si>
+  <si>
+    <t>0.0009,0.0019,0.9984,0.0005</t>
+  </si>
+  <si>
+    <t>0.1363,0.0044,0.3198,0.5923</t>
+  </si>
+  <si>
+    <t>0.1203,0.0298,0.8657,0.0219</t>
+  </si>
+  <si>
+    <t>0.0363,0.0145,0.9534,0.0121</t>
+  </si>
+  <si>
+    <t>0.7490,0.0007,0.0027,0.4127</t>
+  </si>
+  <si>
+    <t>0.0086,0.2473,0.0069,0.9847</t>
+  </si>
+  <si>
+    <t>0.1199,0.0073,0.0006,0.9612</t>
+  </si>
+  <si>
+    <t>0.0133,0.0004,0.0008,0.9943</t>
+  </si>
+  <si>
+    <t>0.0062,0.0003,0.0013,0.9954</t>
+  </si>
+  <si>
+    <t>0.8038,0.0266,0.0762,0.0894</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1959,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1976,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2032,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2102,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2127,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2186,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2312,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2354,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2379,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2435,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2477,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2578,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2813,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2844,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2858,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2872,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2886,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2928,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2939,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3107,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3121,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3135,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3149,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3236,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3432,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3460,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3474,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3488,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3558,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3583,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3600,7 @@
         <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3667,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3709,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3796,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3852,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3891,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3905,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3919,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3933,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4003,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4087,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4129,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4157,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4353,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4367,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4381,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4395,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4468,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4496,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4535,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4552,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4566,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4591,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4622,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4633,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4647,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4675,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4692,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4703,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4717,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4731,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4815,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4829,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4916,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5039,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5056,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5070,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5165,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5336,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5403,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5420,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5434,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5448,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5462,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5476,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5490,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5504,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5515,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
   </sheetData>
